--- a/template/assets/asset_import_template_v1.xlsx
+++ b/template/assets/asset_import_template_v1.xlsx
@@ -414,16 +414,8 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>税额</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>规格补充</t>
-        </is>
-      </c>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
